--- a/manager_forms/002_remote_work_survey--manager_forms.xlsx
+++ b/manager_forms/002_remote_work_survey--manager_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1240,8 +1240,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'option2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'option2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'option_3',_'value':_'option3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3', 'value': 'option3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'option2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'option2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'option_3',_'value':_'option3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3', 'value': 'option3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'option2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'option_3',_'value':_'option3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3', 'value': 'option3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'option2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'option2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'option_3',_'value':_'option3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3', 'value': 'option3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1779,12 +1779,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
